--- a/models/modelofacefotos.xlsx
+++ b/models/modelofacefotos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\eclipse-workspace\GeradorRelatorio\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AC6537-F943-4028-9E2F-618E1833A3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914DF930-69B3-4E71-8ECB-49444BA328F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan2" sheetId="2" r:id="rId1"/>
@@ -206,15 +206,15 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -585,12 +585,12 @@
       <c r="D3" s="8"/>
       <c r="E3" s="11"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="14"/>
+      <c r="H3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
@@ -846,7 +846,7 @@
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
-      <c r="B25" s="17"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
@@ -924,7 +924,7 @@
   <pageMargins left="0.27559055118110237" right="0.27559055118110237" top="0.51181102362204722" bottom="0.51181102362204722" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddHeader xml:space="preserve">&amp;C&amp;"Algerian,Regular"&amp;16FACE E FOTOS  2025
+    <oddHeader xml:space="preserve">&amp;C&amp;"Algerian,Regular"&amp;16A FACE E FOTOS  2025
 </oddHeader>
   </headerFooter>
 </worksheet>
